--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>100</v>
       </c>
       <c r="F15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="L15" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
-        <v>133.333333333333</v>
+        <v>80</v>
       </c>
       <c r="N15" s="14">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="F16" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>29.411764705882</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I16" s="15">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J16" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K16" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-46</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-51.785714285714</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.142857142857</v>
+        <v>-85.833333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G17" s="15">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H17" s="14">
-        <v>-23.809523809523</v>
+        <v>2.631578947368</v>
       </c>
       <c r="I17" s="15">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K17" s="14">
-        <v>-14.516129032258</v>
+        <v>-8.450704225352</v>
       </c>
       <c r="L17" s="14">
-        <v>-17.1875</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>96.296296296296</v>
+        <v>124.137931034483</v>
       </c>
       <c r="N17" s="14">
-        <v>43.243243243243</v>
+        <v>51.162790697674</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="F18" s="15">
         <v>7</v>
       </c>
       <c r="G18" s="15">
+        <v>20</v>
+      </c>
+      <c r="H18" s="14">
+        <v>-65</v>
+      </c>
+      <c r="I18" s="15">
         <v>13</v>
       </c>
-      <c r="H18" s="14">
-        <v>-46.153846153846</v>
-      </c>
-      <c r="I18" s="15">
-        <v>12</v>
-      </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K18" s="14">
-        <v>-40</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="L18" s="14">
-        <v>-65.714285714285</v>
+        <v>-71.111111111111</v>
       </c>
       <c r="M18" s="14">
-        <v>-72.093023255813</v>
+        <v>-75</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.818815331010</v>
+        <v>-96.119402985074</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>13</v>
+      </c>
+      <c r="D19" s="15">
         <v>10</v>
       </c>
-      <c r="D19" s="15">
-        <v>12</v>
-      </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>30</v>
       </c>
       <c r="F19" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G19" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>-10.638297872340</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="I19" s="15">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="J19" s="15">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K19" s="14">
-        <v>-22.619047619047</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="L19" s="14">
-        <v>-46.721311475409</v>
+        <v>-41.843971631205</v>
       </c>
       <c r="M19" s="14">
-        <v>1.5625</v>
+        <v>10.810810810810</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.851851851851</v>
+        <v>-46.405228758169</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D20" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="F20" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" s="14">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-51.612903225806</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M20" s="14">
-        <v>-11.764705882352</v>
+        <v>10</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.163424124513</v>
+        <v>-92.439862542955</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>5.555555555555</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G21" s="17">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.518796992481</v>
+        <v>2.898550724637</v>
       </c>
       <c r="I21" s="17">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="J21" s="17">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.511520737327</v>
+        <v>-12.109375</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.883116883116</v>
+        <v>-37.845303867403</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.761904761904</v>
+        <v>-6.25</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.793991416309</v>
+        <v>-78.952291861552</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>33.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
         <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>-16.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L22" s="14">
-        <v>-28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E24" s="14">
-        <v>-57.446808510638</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="15">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G24" s="15">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="H24" s="14">
-        <v>-15.934065934065</v>
+        <v>-22.842639593908</v>
       </c>
       <c r="I24" s="15">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="J24" s="15">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="K24" s="14">
-        <v>-13.147410358565</v>
+        <v>-18.987341772151</v>
       </c>
       <c r="L24" s="14">
-        <v>-40.599455040871</v>
+        <v>-41.013824884792</v>
       </c>
       <c r="M24" s="14">
-        <v>43.421052631578</v>
+        <v>43.820224719101</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D25" s="15">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E25" s="14">
-        <v>-72.5</v>
+        <v>-51.923076923076</v>
       </c>
       <c r="F25" s="15">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G25" s="15">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="H25" s="14">
-        <v>-22.222222222222</v>
+        <v>-31.446540880503</v>
       </c>
       <c r="I25" s="15">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="J25" s="15">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="K25" s="14">
-        <v>-25.757575757575</v>
+        <v>-31.2</v>
       </c>
       <c r="L25" s="14">
-        <v>-49.829351535836</v>
+        <v>-50.716332378223</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E26" s="14">
-        <v>88.888888888888</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G26" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H26" s="14">
-        <v>31.914893617021</v>
+        <v>40.816326530612</v>
       </c>
       <c r="I26" s="15">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="J26" s="15">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K26" s="14">
-        <v>16.867469879518</v>
+        <v>15.841584158415</v>
       </c>
       <c r="L26" s="14">
-        <v>-12.612612612612</v>
+        <v>-15.827338129496</v>
       </c>
       <c r="M26" s="14">
-        <v>83.018867924528</v>
+        <v>91.803278688524</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>100</v>
       </c>
       <c r="F27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G27" s="15">
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L27" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H28" s="14">
-        <v>-73.333333333333</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
         <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>-56.25</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
-        <v>-53.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>7</v>
@@ -911,22 +911,22 @@
         <v>250</v>
       </c>
       <c r="I15" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="N15" s="14">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>85.714285714285</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="15">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J16" s="15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L16" s="14">
-        <v>-43.333333333333</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="M16" s="14">
-        <v>-43.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.833333333333</v>
+        <v>-82.879377431906</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>12</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>39</v>
       </c>
       <c r="G17" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H17" s="14">
-        <v>2.631578947368</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="J17" s="15">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K17" s="14">
-        <v>-8.450704225352</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="L17" s="14">
-        <v>-13.333333333333</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M17" s="14">
-        <v>124.137931034483</v>
+        <v>145.161290322581</v>
       </c>
       <c r="N17" s="14">
-        <v>51.162790697674</v>
+        <v>46.153846153846</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>11</v>
-      </c>
       <c r="E18" s="14">
-        <v>-90.909090909090</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H18" s="14">
-        <v>-65</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J18" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="14">
-        <v>-58.064516129032</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>-71.111111111111</v>
+        <v>-68</v>
       </c>
       <c r="M18" s="14">
-        <v>-75</v>
+        <v>-74.193548387096</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.119402985074</v>
+        <v>-95.778364116095</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F19" s="15">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G19" s="15">
         <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>-8.163265306122</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J19" s="15">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K19" s="14">
-        <v>-12.765957446808</v>
+        <v>-16.190476190476</v>
       </c>
       <c r="L19" s="14">
-        <v>-41.843971631205</v>
+        <v>-46.012269938650</v>
       </c>
       <c r="M19" s="14">
-        <v>10.810810810810</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="N19" s="14">
-        <v>-46.405228758169</v>
+        <v>-47.928994082840</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>4</v>
+      </c>
+      <c r="D20" s="15">
         <v>7</v>
       </c>
-      <c r="D20" s="15">
-        <v>4</v>
-      </c>
       <c r="E20" s="14">
-        <v>75</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H20" s="14">
-        <v>20</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I20" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J20" s="15">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L20" s="14">
-        <v>-35.294117647058</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="M20" s="14">
-        <v>10</v>
+        <v>13.636363636363</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.439862542955</v>
+        <v>-92.559523809523</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H21" s="18">
-        <v>2.898550724637</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="I21" s="17">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="J21" s="17">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.109375</v>
+        <v>-11.262798634812</v>
       </c>
       <c r="L21" s="18">
-        <v>-37.845303867403</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.25</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.952291861552</v>
+        <v>-78.351373855120</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,34 +1180,34 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>166.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I22" s="15">
         <v>9</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L22" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E24" s="14">
-        <v>-40</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="F24" s="15">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="G24" s="15">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H24" s="14">
-        <v>-22.842639593908</v>
+        <v>-37.244897959183</v>
       </c>
       <c r="I24" s="15">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="J24" s="15">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="K24" s="14">
-        <v>-18.987341772151</v>
+        <v>-25.815217391304</v>
       </c>
       <c r="L24" s="14">
-        <v>-41.013824884792</v>
+        <v>-44.285714285714</v>
       </c>
       <c r="M24" s="14">
-        <v>43.820224719101</v>
+        <v>36.5</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D25" s="15">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E25" s="14">
-        <v>-51.923076923076</v>
+        <v>-64.444444444444</v>
       </c>
       <c r="F25" s="15">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="G25" s="15">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H25" s="14">
-        <v>-31.446540880503</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I25" s="15">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="J25" s="15">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.2</v>
+        <v>-36.271186440678</v>
       </c>
       <c r="L25" s="14">
-        <v>-50.716332378223</v>
+        <v>-52.882205513784</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D26" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E26" s="14">
-        <v>16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G26" s="15">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H26" s="14">
-        <v>40.816326530612</v>
+        <v>47.272727272727</v>
       </c>
       <c r="I26" s="15">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="J26" s="15">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="K26" s="14">
-        <v>15.841584158415</v>
+        <v>24.347826086956</v>
       </c>
       <c r="L26" s="14">
-        <v>-15.827338129496</v>
+        <v>-15.882352941176</v>
       </c>
       <c r="M26" s="14">
-        <v>91.803278688524</v>
+        <v>93.243243243243</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>7</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="I27" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>80</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="15">
+        <v>4</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-25</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H28" s="14">
-        <v>-58.333333333333</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="L28" s="14">
-        <v>-55.555555555555</v>
+        <v>-45</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
         <v>11</v>
@@ -920,7 +920,7 @@
         <v>175</v>
       </c>
       <c r="L15" s="14">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M15" s="14">
         <v>120</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>-37.5</v>
       </c>
       <c r="F16" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="I16" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J16" s="15">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K16" s="14">
-        <v>10</v>
+        <v>2.083333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-37.142857142857</v>
+        <v>-42.352941176470</v>
       </c>
       <c r="M16" s="14">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="N16" s="14">
-        <v>-82.879377431906</v>
+        <v>-82.624113475177</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D17" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G17" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H17" s="14">
-        <v>-7.142857142857</v>
+        <v>6.382978723404</v>
       </c>
       <c r="I17" s="15">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="J17" s="15">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K17" s="14">
-        <v>-8.433734939759</v>
+        <v>-5.102040816326</v>
       </c>
       <c r="L17" s="14">
-        <v>-11.627906976744</v>
+        <v>-4.123711340206</v>
       </c>
       <c r="M17" s="14">
-        <v>145.161290322581</v>
+        <v>158.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>46.153846153846</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>-72.222222222222</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I18" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="14">
-        <v>-50</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="L18" s="14">
-        <v>-68</v>
+        <v>-67.241379310344</v>
       </c>
       <c r="M18" s="14">
-        <v>-74.193548387096</v>
+        <v>-73.611111111111</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.778364116095</v>
+        <v>-95.662100456621</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-27.272727272727</v>
+        <v>30</v>
       </c>
       <c r="F19" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="15">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.285714285714</v>
+        <v>2.325581395348</v>
       </c>
       <c r="I19" s="15">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J19" s="15">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="K19" s="14">
-        <v>-16.190476190476</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L19" s="14">
-        <v>-46.012269938650</v>
+        <v>-47.089947089947</v>
       </c>
       <c r="M19" s="14">
-        <v>-2.222222222222</v>
+        <v>1.010101010101</v>
       </c>
       <c r="N19" s="14">
-        <v>-47.928994082840</v>
+        <v>-44.134078212290</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>5</v>
+      </c>
+      <c r="D20" s="15">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
-        <v>7</v>
-      </c>
       <c r="E20" s="14">
-        <v>-42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="F20" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G20" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H20" s="14">
-        <v>-31.578947368421</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I20" s="15">
+        <v>30</v>
+      </c>
+      <c r="J20" s="15">
+        <v>33</v>
+      </c>
+      <c r="K20" s="14">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="L20" s="14">
+        <v>-31.818181818181</v>
+      </c>
+      <c r="M20" s="14">
         <v>25</v>
       </c>
-      <c r="J20" s="15">
-        <v>29</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-13.793103448275</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-35.897435897435</v>
-      </c>
-      <c r="M20" s="14">
-        <v>13.636363636363</v>
-      </c>
       <c r="N20" s="14">
-        <v>-92.559523809523</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="G21" s="17">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.849315068493</v>
+        <v>3.289473684210</v>
       </c>
       <c r="I21" s="17">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="J21" s="17">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.262798634812</v>
+        <v>-9.309309309309</v>
       </c>
       <c r="L21" s="18">
-        <v>-37.349397590361</v>
+        <v>-37.214137214137</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.797101449275</v>
+        <v>-1.307189542483</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.351373855120</v>
+        <v>-77.529761904761</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>133.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I22" s="15">
         <v>9</v>
       </c>
       <c r="J22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D24" s="15">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E24" s="14">
-        <v>-63.461538461538</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="F24" s="15">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G24" s="15">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H24" s="14">
-        <v>-37.244897959183</v>
+        <v>-44.497607655502</v>
       </c>
       <c r="I24" s="15">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="J24" s="15">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.815217391304</v>
+        <v>-24.697336561743</v>
       </c>
       <c r="L24" s="14">
-        <v>-44.285714285714</v>
+        <v>-47.466216216216</v>
       </c>
       <c r="M24" s="14">
-        <v>36.5</v>
+        <v>35.807860262008</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D25" s="15">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E25" s="14">
-        <v>-64.444444444444</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="F25" s="15">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G25" s="15">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H25" s="14">
-        <v>-44.444444444444</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I25" s="15">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="J25" s="15">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="K25" s="14">
-        <v>-36.271186440678</v>
+        <v>-36.636636636636</v>
       </c>
       <c r="L25" s="14">
-        <v>-52.882205513784</v>
+        <v>-56.224066390041</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D26" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>26.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G26" s="15">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="14">
-        <v>47.272727272727</v>
+        <v>46.428571428571</v>
       </c>
       <c r="I26" s="15">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J26" s="15">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="K26" s="14">
-        <v>24.347826086956</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L26" s="14">
-        <v>-15.882352941176</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M26" s="14">
-        <v>93.243243243243</v>
+        <v>88.235294117647</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>7</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>75</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="15">
         <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
-        <v>83.333333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>7</v>
       </c>
       <c r="G28" s="15">
+        <v>9</v>
+      </c>
+      <c r="H28" s="14">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="I28" s="15">
         <v>13</v>
       </c>
-      <c r="H28" s="14">
-        <v>-46.153846153846</v>
-      </c>
-      <c r="I28" s="15">
-        <v>11</v>
-      </c>
       <c r="J28" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="14">
-        <v>-45</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L28" s="14">
-        <v>-45</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I15" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L15" s="14">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M15" s="14">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N15" s="14">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H16" s="14">
-        <v>60</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J16" s="15">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K16" s="14">
-        <v>2.083333333333</v>
+        <v>-1.851851851851</v>
       </c>
       <c r="L16" s="14">
-        <v>-42.352941176470</v>
+        <v>-42.391304347826</v>
       </c>
       <c r="M16" s="14">
-        <v>-30</v>
+        <v>-31.168831168831</v>
       </c>
       <c r="N16" s="14">
-        <v>-82.624113475177</v>
+        <v>-82.679738562091</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E17" s="14">
-        <v>6.666666666666</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F17" s="15">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G17" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H17" s="14">
-        <v>6.382978723404</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="I17" s="15">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J17" s="15">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.102040816326</v>
+        <v>-9.909909909909</v>
       </c>
       <c r="L17" s="14">
-        <v>-4.123711340206</v>
+        <v>-8.256880733944</v>
       </c>
       <c r="M17" s="14">
-        <v>158.333333333333</v>
+        <v>143.90243902439</v>
       </c>
       <c r="N17" s="14">
-        <v>50</v>
+        <v>40.845070422535</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-57.894736842105</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="15">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K18" s="14">
-        <v>-45.714285714285</v>
+        <v>-48.780487804878</v>
       </c>
       <c r="L18" s="14">
-        <v>-67.241379310344</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-73.611111111111</v>
+        <v>-73.417721518987</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.662100456621</v>
+        <v>-95.643153526970</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E19" s="14">
-        <v>30</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F19" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="15">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H19" s="14">
-        <v>2.325581395348</v>
+        <v>-4</v>
       </c>
       <c r="I19" s="15">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J19" s="15">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.043478260869</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="L19" s="14">
-        <v>-47.089947089947</v>
+        <v>-43.137254901960</v>
       </c>
       <c r="M19" s="14">
-        <v>1.010101010101</v>
+        <v>4.504504504504</v>
       </c>
       <c r="N19" s="14">
-        <v>-44.134078212290</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>5</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>25</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G20" s="15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H20" s="14">
-        <v>-19.047619047619</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I20" s="15">
         <v>30</v>
       </c>
       <c r="J20" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K20" s="14">
-        <v>-9.090909090909</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L20" s="14">
-        <v>-31.818181818181</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="M20" s="14">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-92</v>
+        <v>-92.822966507177</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>7.5</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="F21" s="17">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H21" s="18">
-        <v>3.289473684210</v>
+        <v>-10.909090909090</v>
       </c>
       <c r="I21" s="17">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="J21" s="17">
-        <v>333</v>
+        <v>382</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.309309309309</v>
+        <v>-13.089005235602</v>
       </c>
       <c r="L21" s="18">
-        <v>-37.214137214137</v>
+        <v>-36.761904761904</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.307189542483</v>
+        <v>-2.352941176470</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.529761904761</v>
+        <v>-77.733065057008</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="15">
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="15">
+        <v>10</v>
+      </c>
+      <c r="J22" s="15">
         <v>9</v>
       </c>
-      <c r="J22" s="15">
-        <v>8</v>
-      </c>
       <c r="K22" s="14">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D24" s="15">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E24" s="14">
-        <v>-15.555555555555</v>
+        <v>-25.454545454545</v>
       </c>
       <c r="F24" s="15">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="G24" s="15">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="H24" s="14">
-        <v>-44.497607655502</v>
+        <v>-36.866359447004</v>
       </c>
       <c r="I24" s="15">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="J24" s="15">
-        <v>413</v>
+        <v>468</v>
       </c>
       <c r="K24" s="14">
-        <v>-24.697336561743</v>
+        <v>-24.786324786324</v>
       </c>
       <c r="L24" s="14">
-        <v>-47.466216216216</v>
+        <v>-46.177370030581</v>
       </c>
       <c r="M24" s="14">
-        <v>35.807860262008</v>
+        <v>32.830188679245</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D25" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E25" s="14">
-        <v>-39.473684210526</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F25" s="15">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G25" s="15">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H25" s="14">
-        <v>-57.142857142857</v>
+        <v>-48.587570621468</v>
       </c>
       <c r="I25" s="15">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="J25" s="15">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="K25" s="14">
-        <v>-36.636636636636</v>
+        <v>-36.533333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>-56.224066390041</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
         <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>26.666666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G26" s="15">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H26" s="14">
-        <v>46.428571428571</v>
+        <v>24.193548387096</v>
       </c>
       <c r="I26" s="15">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="J26" s="15">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="K26" s="14">
-        <v>23.076923076923</v>
+        <v>17.931034482758</v>
       </c>
       <c r="L26" s="14">
-        <v>-17.948717948717</v>
+        <v>-22.624434389140</v>
       </c>
       <c r="M26" s="14">
-        <v>88.235294117647</v>
+        <v>81.914893617021</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="15">
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L27" s="14">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
+        <v>6</v>
+      </c>
+      <c r="G28" s="15">
         <v>7</v>
       </c>
-      <c r="G28" s="15">
-        <v>9</v>
-      </c>
       <c r="H28" s="14">
-        <v>-22.222222222222</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="15">
         <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="14">
-        <v>-40.909090909090</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L28" s="14">
-        <v>-38.095238095238</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-93.333333333333</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-93.333333333333</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,260 +878,260 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="N14" s="15">
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>5</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="H15" s="15">
+        <v>400</v>
+      </c>
+      <c r="I15" s="14">
+        <v>14</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="14">
-        <v>150</v>
-      </c>
-      <c r="I15" s="15">
-        <v>12</v>
-      </c>
-      <c r="J15" s="15">
-        <v>5</v>
-      </c>
-      <c r="K15" s="14">
-        <v>140</v>
-      </c>
-      <c r="L15" s="14">
-        <v>71.428571428571</v>
-      </c>
-      <c r="M15" s="14">
-        <v>140</v>
-      </c>
-      <c r="N15" s="14">
-        <v>1100</v>
+      <c r="K15" s="15">
+        <v>180</v>
+      </c>
+      <c r="L15" s="15">
+        <v>100</v>
+      </c>
+      <c r="M15" s="15">
+        <v>180</v>
+      </c>
+      <c r="N15" s="15">
+        <v>1300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>4</v>
-      </c>
-      <c r="D16" s="15">
-        <v>6</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F16" s="15">
-        <v>25</v>
-      </c>
-      <c r="G16" s="15">
-        <v>24</v>
-      </c>
-      <c r="H16" s="14">
-        <v>4.166666666666</v>
-      </c>
-      <c r="I16" s="15">
-        <v>53</v>
-      </c>
-      <c r="J16" s="15">
-        <v>54</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-1.851851851851</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-42.391304347826</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-31.168831168831</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-82.679738562091</v>
+      <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
+        <v>10</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>23</v>
+      </c>
+      <c r="G16" s="14">
+        <v>30</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-23.333333333333</v>
+      </c>
+      <c r="I16" s="14">
+        <v>58</v>
+      </c>
+      <c r="J16" s="14">
+        <v>64</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-9.375</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-44.761904761904</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-34.090909090909</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-81.987577639751</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>6</v>
-      </c>
-      <c r="D17" s="15">
-        <v>13</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-53.846153846153</v>
-      </c>
-      <c r="F17" s="15">
+      <c r="C17" s="14">
+        <v>11</v>
+      </c>
+      <c r="D17" s="14">
+        <v>22</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F17" s="14">
         <v>46</v>
       </c>
-      <c r="G17" s="15">
-        <v>49</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-6.122448979591</v>
-      </c>
-      <c r="I17" s="15">
-        <v>100</v>
-      </c>
-      <c r="J17" s="15">
-        <v>111</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-9.909909909909</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-8.256880733944</v>
-      </c>
-      <c r="M17" s="14">
-        <v>143.90243902439</v>
-      </c>
-      <c r="N17" s="14">
-        <v>40.845070422535</v>
+      <c r="G17" s="14">
+        <v>62</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-25.806451612903</v>
+      </c>
+      <c r="I17" s="14">
+        <v>112</v>
+      </c>
+      <c r="J17" s="14">
+        <v>133</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-15.789473684210</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="M17" s="15">
+        <v>115.384615384615</v>
+      </c>
+      <c r="N17" s="15">
+        <v>45.454545454545</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>6</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="15">
-        <v>8</v>
-      </c>
-      <c r="G18" s="15">
-        <v>21</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-61.904761904761</v>
-      </c>
-      <c r="I18" s="15">
-        <v>21</v>
-      </c>
-      <c r="J18" s="15">
-        <v>41</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-48.780487804878</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-73.417721518987</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-95.643153526970</v>
+      <c r="D18" s="14">
+        <v>5</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
+        <v>15</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-40</v>
+      </c>
+      <c r="I18" s="14">
+        <v>23</v>
+      </c>
+      <c r="J18" s="14">
+        <v>46</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-65.671641791044</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-75.268817204301</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-95.676691729323</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>13</v>
-      </c>
-      <c r="D19" s="15">
-        <v>19</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-31.578947368421</v>
-      </c>
-      <c r="F19" s="15">
+      <c r="C19" s="14">
+        <v>14</v>
+      </c>
+      <c r="D19" s="14">
+        <v>15</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-6.666666666666</v>
+      </c>
+      <c r="F19" s="14">
         <v>48</v>
       </c>
-      <c r="G19" s="15">
-        <v>50</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-4</v>
-      </c>
-      <c r="I19" s="15">
-        <v>116</v>
-      </c>
-      <c r="J19" s="15">
-        <v>134</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-13.432835820895</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-43.137254901960</v>
-      </c>
-      <c r="M19" s="14">
-        <v>4.504504504504</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-42.857142857142</v>
+      <c r="G19" s="14">
+        <v>55</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-12.727272727272</v>
+      </c>
+      <c r="I19" s="14">
+        <v>129</v>
+      </c>
+      <c r="J19" s="14">
+        <v>149</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-13.422818791946</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-42.152466367713</v>
+      </c>
+      <c r="M19" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-40.825688073394</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
-        <v>4</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>15</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="C20" s="14">
+        <v>10</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>900</v>
+      </c>
+      <c r="F20" s="14">
         <v>19</v>
       </c>
-      <c r="H20" s="14">
-        <v>-21.052631578947</v>
-      </c>
-      <c r="I20" s="15">
-        <v>30</v>
-      </c>
-      <c r="J20" s="15">
-        <v>37</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-18.918918918918</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-38.775510204081</v>
-      </c>
-      <c r="M20" s="14">
-        <v>11.111111111111</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-92.822966507177</v>
+      <c r="G20" s="14">
+        <v>16</v>
+      </c>
+      <c r="H20" s="15">
+        <v>18.75</v>
+      </c>
+      <c r="I20" s="14">
+        <v>40</v>
+      </c>
+      <c r="J20" s="14">
+        <v>38</v>
+      </c>
+      <c r="K20" s="15">
+        <v>5.263157894736</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="M20" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-91.111111111111</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,77 +1139,77 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.938775510204</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G21" s="17">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.909090909090</v>
+        <v>-15.642458100558</v>
       </c>
       <c r="I21" s="17">
-        <v>332</v>
+        <v>377</v>
       </c>
       <c r="J21" s="17">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.089005235602</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-36.761904761904</v>
+        <v>-35.334476843910</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.352941176470</v>
+        <v>-2.835051546391</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.733065057008</v>
+        <v>-76.583850931677</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I22" s="14">
+        <v>10</v>
+      </c>
+      <c r="J22" s="14">
+        <v>10</v>
+      </c>
+      <c r="K22" s="15">
         <v>0</v>
       </c>
-      <c r="F22" s="15">
-        <v>4</v>
-      </c>
-      <c r="G22" s="15">
-        <v>3</v>
-      </c>
-      <c r="H22" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="I22" s="15">
-        <v>10</v>
-      </c>
-      <c r="J22" s="15">
-        <v>9</v>
-      </c>
-      <c r="K22" s="14">
-        <v>11.111111111111</v>
-      </c>
-      <c r="L22" s="14">
-        <v>0</v>
-      </c>
-      <c r="M22" s="14">
+      <c r="L22" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="M22" s="15">
         <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>41</v>
-      </c>
-      <c r="D24" s="15">
-        <v>55</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-25.454545454545</v>
-      </c>
-      <c r="F24" s="15">
-        <v>137</v>
-      </c>
-      <c r="G24" s="15">
-        <v>217</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-36.866359447004</v>
-      </c>
-      <c r="I24" s="15">
-        <v>352</v>
-      </c>
-      <c r="J24" s="15">
-        <v>468</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-24.786324786324</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-46.177370030581</v>
-      </c>
-      <c r="M24" s="14">
-        <v>32.830188679245</v>
+      <c r="C24" s="14">
+        <v>43</v>
+      </c>
+      <c r="D24" s="14">
+        <v>51</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-15.686274509803</v>
+      </c>
+      <c r="F24" s="14">
+        <v>143</v>
+      </c>
+      <c r="G24" s="14">
+        <v>203</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-29.556650246305</v>
+      </c>
+      <c r="I24" s="14">
+        <v>397</v>
+      </c>
+      <c r="J24" s="14">
+        <v>519</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-23.506743737957</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-44.241573033707</v>
+      </c>
+      <c r="M24" s="15">
+        <v>35.958904109589</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>27</v>
-      </c>
-      <c r="D25" s="15">
-        <v>42</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="F25" s="15">
-        <v>91</v>
-      </c>
-      <c r="G25" s="15">
-        <v>177</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-48.587570621468</v>
-      </c>
-      <c r="I25" s="15">
-        <v>238</v>
-      </c>
-      <c r="J25" s="15">
-        <v>375</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-36.533333333333</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-55.263157894736</v>
+      <c r="C25" s="14">
+        <v>32</v>
+      </c>
+      <c r="D25" s="14">
+        <v>41</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-21.951219512195</v>
+      </c>
+      <c r="F25" s="14">
+        <v>99</v>
+      </c>
+      <c r="G25" s="14">
+        <v>166</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-40.361445783132</v>
+      </c>
+      <c r="I25" s="14">
+        <v>271</v>
+      </c>
+      <c r="J25" s="14">
+        <v>416</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-34.855769230769</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-53.436426116838</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>13</v>
-      </c>
-      <c r="D26" s="15">
-        <v>15</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-13.333333333333</v>
-      </c>
-      <c r="F26" s="15">
-        <v>77</v>
-      </c>
-      <c r="G26" s="15">
-        <v>62</v>
-      </c>
-      <c r="H26" s="14">
-        <v>24.193548387096</v>
-      </c>
-      <c r="I26" s="15">
-        <v>171</v>
-      </c>
-      <c r="J26" s="15">
-        <v>145</v>
-      </c>
-      <c r="K26" s="14">
-        <v>17.931034482758</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-22.624434389140</v>
-      </c>
-      <c r="M26" s="14">
-        <v>81.914893617021</v>
+      <c r="C26" s="14">
+        <v>19</v>
+      </c>
+      <c r="D26" s="14">
+        <v>24</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-20.833333333333</v>
+      </c>
+      <c r="F26" s="14">
+        <v>76</v>
+      </c>
+      <c r="G26" s="14">
+        <v>68</v>
+      </c>
+      <c r="H26" s="15">
+        <v>11.764705882352</v>
+      </c>
+      <c r="I26" s="14">
+        <v>189</v>
+      </c>
+      <c r="J26" s="14">
+        <v>169</v>
+      </c>
+      <c r="K26" s="15">
+        <v>11.834319526627</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-21.25</v>
+      </c>
+      <c r="M26" s="15">
+        <v>64.347826086956</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="E27" s="15">
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
         <v>6</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>100</v>
       </c>
-      <c r="I27" s="15">
-        <v>13</v>
-      </c>
-      <c r="J27" s="15">
-        <v>7</v>
-      </c>
-      <c r="K27" s="14">
-        <v>85.714285714285</v>
-      </c>
-      <c r="L27" s="14">
-        <v>85.714285714285</v>
+      <c r="I27" s="14">
+        <v>15</v>
+      </c>
+      <c r="J27" s="14">
+        <v>8</v>
+      </c>
+      <c r="K27" s="15">
+        <v>87.5</v>
+      </c>
+      <c r="L27" s="15">
+        <v>114.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>6</v>
-      </c>
-      <c r="G28" s="15">
-        <v>7</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I28" s="15">
-        <v>13</v>
-      </c>
-      <c r="J28" s="15">
-        <v>23</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-43.478260869565</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-45.833333333333</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
+        <v>11</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-27.272727272727</v>
+      </c>
+      <c r="I28" s="14">
+        <v>16</v>
+      </c>
+      <c r="J28" s="14">
+        <v>27</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-40.740740740740</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-36</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,90 +1466,90 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="15">
+      <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="15">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
+      </c>
+      <c r="I29" s="14">
+        <v>2</v>
+      </c>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-94.444444444444</v>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="15">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="15">
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
+      </c>
+      <c r="I30" s="14">
+        <v>2</v>
+      </c>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="14">
-        <v>-94.117647058823</v>
+      <c r="M30" s="15">
+        <v>100</v>
+      </c>
+      <c r="N30" s="15">
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,7 +1557,7 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="14">
         <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
@@ -1566,7 +1566,7 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
@@ -1625,7 +1625,7 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>36</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>29</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>11</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>9</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>5</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-44.444444444444</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-54.545454545454</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-82.758620689655</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-86.111111111111</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>42</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>34</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>27</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>44</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>46</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>4.545454545454</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>70.370370370370</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>35.294117647058</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>9.523809523809</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1814</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1541</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>718</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>614</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>439</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-28.501628664495</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-38.857938718663</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-71.512005191434</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-75.799338478500</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>396</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>497</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>383</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>315</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>607</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>92.698412698412</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>58.485639686684</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>22.132796780684</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>53.282828282828</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1976</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>2165</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>720</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>485</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>170</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-64.948453608247</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-76.388888888888</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-92.147806004618</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-91.396761133603</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1547</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1280</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>665</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>605</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>755</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>24.793388429752</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>13.533834586466</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-41.015625</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-51.195862960568</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>3009</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>2302</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>814</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>493</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>253</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-48.681541582150</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-68.918918918918</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-89.009556907037</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-91.591890993685</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -879,7 +879,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>5</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>400</v>
+        <v>-40</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>180</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="M15" s="15">
-        <v>180</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>1300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.333333333333</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="I16" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.375</v>
+        <v>-13.698630136986</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.761904761904</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.090909090909</v>
+        <v>-34.375</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.987577639751</v>
+        <v>-82.451253481894</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,13 +975,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
         <v>46</v>
@@ -993,22 +993,22 @@
         <v>-25.806451612903</v>
       </c>
       <c r="I17" s="14">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="J17" s="14">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.789473684210</v>
+        <v>-13.103448275862</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.5</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="M17" s="15">
-        <v>115.384615384615</v>
+        <v>125</v>
       </c>
       <c r="N17" s="15">
-        <v>45.454545454545</v>
+        <v>44.827586206896</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,10 +1019,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
@@ -1034,22 +1034,22 @@
         <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-46.808510638297</v>
       </c>
       <c r="L18" s="15">
-        <v>-65.671641791044</v>
+        <v>-65.277777777777</v>
       </c>
       <c r="M18" s="15">
-        <v>-75.268817204301</v>
+        <v>-74.489795918367</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.676691729323</v>
+        <v>-95.575221238938</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-6.666666666666</v>
+        <v>69.230769230769</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.727272727272</v>
+        <v>8.771929824561</v>
       </c>
       <c r="I19" s="14">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="J19" s="14">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.422818791946</v>
+        <v>-6.790123456790</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.152466367713</v>
+        <v>-36.820083682008</v>
       </c>
       <c r="M19" s="15">
-        <v>7.5</v>
+        <v>15.267175572519</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.825688073394</v>
+        <v>-37.344398340249</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>18.75</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K20" s="15">
-        <v>5.263157894736</v>
+        <v>4.878048780487</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.076923076923</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="M20" s="15">
-        <v>33.333333333333</v>
+        <v>30.303030303030</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.111111111111</v>
+        <v>-91.188524590163</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.094339622641</v>
+        <v>4.651162790697</v>
       </c>
       <c r="F21" s="17">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G21" s="17">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.642458100558</v>
+        <v>-14.130434782608</v>
       </c>
       <c r="I21" s="17">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="J21" s="17">
-        <v>435</v>
+        <v>477</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.333333333333</v>
+        <v>-11.530398322851</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.334476843910</v>
+        <v>-35.276073619631</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.835051546391</v>
+        <v>0.476190476190</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.583850931677</v>
+        <v>-75.899486007995</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.686274509803</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="G24" s="14">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.556650246305</v>
+        <v>-15.544041450777</v>
       </c>
       <c r="I24" s="14">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="J24" s="14">
-        <v>519</v>
+        <v>561</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.506743737957</v>
+        <v>-22.103386809269</v>
       </c>
       <c r="L24" s="15">
-        <v>-44.241573033707</v>
+        <v>-43.467011642949</v>
       </c>
       <c r="M24" s="15">
-        <v>35.958904109589</v>
+        <v>33.639143730886</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.951219512195</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="F25" s="14">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G25" s="14">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.361445783132</v>
+        <v>-28.481012658227</v>
       </c>
       <c r="I25" s="14">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="J25" s="14">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.855769230769</v>
+        <v>-33.554083885209</v>
       </c>
       <c r="L25" s="15">
-        <v>-53.436426116838</v>
+        <v>-52.222222222222</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>-20.833333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G26" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>11.764705882352</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="J26" s="14">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="K26" s="15">
-        <v>11.834319526627</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.25</v>
+        <v>-20.152091254752</v>
       </c>
       <c r="M26" s="15">
-        <v>64.347826086956</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
         <v>6</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>87.5</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>114.285714285714</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>4</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-25</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-27.272727272727</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>27</v>
       </c>
       <c r="K28" s="15">
-        <v>-40.740740740740</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="L28" s="15">
-        <v>-36</v>
+        <v>-32</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1485,22 +1485,22 @@
         <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
@@ -1526,22 +1526,22 @@
         <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.235294117647</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -881,11 +881,11 @@
       <c r="L14" s="15">
         <v>-50</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
         <v>13</v>
@@ -923,10 +923,10 @@
         <v>62.5</v>
       </c>
       <c r="M15" s="15">
-        <v>116.666666666667</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N15" s="15">
-        <v>1200</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
         <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H16" s="15">
-        <v>-42.424242424242</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J16" s="14">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.698630136986</v>
+        <v>-16.867469879518</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.736842105263</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.375</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.451253481894</v>
+        <v>-82.397959183673</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>-25.806451612903</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="I17" s="14">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J17" s="14">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.103448275862</v>
+        <v>-7.947019867549</v>
       </c>
       <c r="L17" s="15">
-        <v>-20.754716981132</v>
+        <v>-18.235294117647</v>
       </c>
       <c r="M17" s="15">
-        <v>125</v>
+        <v>124.193548387097</v>
       </c>
       <c r="N17" s="15">
-        <v>44.827586206896</v>
+        <v>44.791666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.808510638297</v>
+        <v>-43.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-65.277777777777</v>
+        <v>-67.073170731707</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.489795918367</v>
+        <v>-73.786407766990</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.575221238938</v>
+        <v>-95.514950166113</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>69.230769230769</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H19" s="15">
-        <v>8.771929824561</v>
+        <v>-14.0625</v>
       </c>
       <c r="I19" s="14">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J19" s="14">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.790123456790</v>
+        <v>-11.731843575419</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.820083682008</v>
+        <v>-37.301587301587</v>
       </c>
       <c r="M19" s="15">
-        <v>15.267175572519</v>
+        <v>12.056737588652</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.344398340249</v>
+        <v>-40.601503759398</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>77.777777777777</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>4.878048780487</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.862068965517</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M20" s="15">
-        <v>30.303030303030</v>
+        <v>35.294117647058</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.188524590163</v>
+        <v>-91.221374045801</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>4.651162790697</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="G21" s="17">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.130434782608</v>
+        <v>-18.994413407821</v>
       </c>
       <c r="I21" s="17">
-        <v>422</v>
+        <v>453</v>
       </c>
       <c r="J21" s="17">
-        <v>477</v>
+        <v>512</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.530398322851</v>
+        <v>-11.5234375</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.276073619631</v>
+        <v>-35.470085470085</v>
       </c>
       <c r="M21" s="18">
-        <v>0.476190476190</v>
+        <v>0.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.899486007995</v>
+        <v>-76.069730586370</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-8.333333333333</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L22" s="15">
-        <v>-15.384615384615</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.761904761904</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="F24" s="14">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G24" s="14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.544041450777</v>
+        <v>-13.846153846153</v>
       </c>
       <c r="I24" s="14">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="J24" s="14">
-        <v>561</v>
+        <v>608</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.103386809269</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L24" s="15">
-        <v>-43.467011642949</v>
+        <v>-41.248470012239</v>
       </c>
       <c r="M24" s="15">
-        <v>33.639143730886</v>
+        <v>34.453781512605</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" s="15">
-        <v>-18.918918918918</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="F25" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G25" s="14">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.481012658227</v>
+        <v>-23.717948717948</v>
       </c>
       <c r="I25" s="14">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="J25" s="14">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.554083885209</v>
+        <v>-32.515337423312</v>
       </c>
       <c r="L25" s="15">
-        <v>-52.222222222222</v>
+        <v>-50.892857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G26" s="14">
         <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.333333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="J26" s="14">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="K26" s="15">
-        <v>10.526315789473</v>
+        <v>15.609756097561</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.152091254752</v>
+        <v>-17.132867132867</v>
       </c>
       <c r="M26" s="15">
-        <v>66.666666666666</v>
+        <v>60.135135135135</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>14</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>6</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>500</v>
       </c>
       <c r="F28" s="14">
+        <v>10</v>
+      </c>
+      <c r="G28" s="14">
         <v>6</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>-37.037037037037</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>-32</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>2</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>44.444444444444</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L15" s="15">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>550</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H16" s="15">
-        <v>-42.857142857142</v>
+        <v>-45</v>
       </c>
       <c r="I16" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J16" s="14">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.867469879518</v>
+        <v>-20.212765957446</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.238095238095</v>
+        <v>-42.748091603053</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.352941176470</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.397959183673</v>
+        <v>-82.014388489208</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>83.333333333333</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.867924528301</v>
+        <v>10.204081632653</v>
       </c>
       <c r="I17" s="14">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="J17" s="14">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.947019867549</v>
+        <v>-1.875</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.235294117647</v>
+        <v>-17.368421052631</v>
       </c>
       <c r="M17" s="15">
-        <v>124.193548387097</v>
+        <v>145.3125</v>
       </c>
       <c r="N17" s="15">
-        <v>44.791666666666</v>
+        <v>53.921568627451</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-38.461538461538</v>
+        <v>-10</v>
       </c>
       <c r="I18" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.75</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L18" s="15">
-        <v>-67.073170731707</v>
+        <v>-65.116279069767</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.786407766990</v>
+        <v>-72.477064220183</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.514950166113</v>
+        <v>-95.398773006135</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.823529411764</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.0625</v>
+        <v>7.017543859649</v>
       </c>
       <c r="I19" s="14">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="J19" s="14">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.731843575419</v>
+        <v>-7.853403141361</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.301587301587</v>
+        <v>-32.046332046332</v>
       </c>
       <c r="M19" s="15">
-        <v>12.056737588652</v>
+        <v>17.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.601503759398</v>
+        <v>-38.675958188153</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>77.777777777777</v>
+        <v>212.5</v>
       </c>
       <c r="I20" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K20" s="15">
-        <v>9.523809523809</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.806451612903</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M20" s="15">
-        <v>35.294117647058</v>
+        <v>48.648648648648</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.221374045801</v>
+        <v>-90.248226950354</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.142857142857</v>
+        <v>34.210526315789</v>
       </c>
       <c r="F21" s="17">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G21" s="17">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.994413407821</v>
+        <v>3.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>453</v>
+        <v>508</v>
       </c>
       <c r="J21" s="17">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.5234375</v>
+        <v>-7.636363636363</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.470085470085</v>
+        <v>-31.443994601889</v>
       </c>
       <c r="M21" s="18">
-        <v>0.666666666666</v>
+        <v>6.054279749478</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.069730586370</v>
+        <v>-75.036855036855</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J22" s="14">
         <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-7.692307692307</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L22" s="15">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.638297872340</v>
+        <v>-28.260869565217</v>
       </c>
       <c r="F24" s="14">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="G24" s="14">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.846153846153</v>
+        <v>-15.053763440860</v>
       </c>
       <c r="I24" s="14">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="J24" s="14">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.052631578947</v>
+        <v>-21.712538226299</v>
       </c>
       <c r="L24" s="15">
-        <v>-41.248470012239</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="M24" s="15">
-        <v>34.453781512605</v>
+        <v>36.170212765957</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" s="15">
-        <v>-19.444444444444</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="F25" s="14">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G25" s="14">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.717948717948</v>
+        <v>-26.351351351351</v>
       </c>
       <c r="I25" s="14">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="J25" s="14">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.515337423312</v>
+        <v>-33.460803059273</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.892857142857</v>
+        <v>-50.568181818181</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>80</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="F26" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>6.666666666666</v>
+        <v>3.488372093023</v>
       </c>
       <c r="I26" s="14">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="J26" s="14">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="K26" s="15">
-        <v>15.609756097561</v>
+        <v>12.121212121212</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.132867132867</v>
+        <v>-17.515923566879</v>
       </c>
       <c r="M26" s="15">
-        <v>60.135135135135</v>
+        <v>62.893081761006</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>55.555555555555</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>500</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>87.5</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K28" s="15">
-        <v>-17.857142857142</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.814814814814</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1552,28 +1552,28 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-75</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>55.555555555555</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-45.454545454545</v>
+        <v>350</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-45</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="I16" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J16" s="14">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.212765957446</v>
+        <v>-12.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.748091603053</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.432432432432</v>
+        <v>-25.663716814159</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.014388489208</v>
+        <v>-80.995475113122</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>77.777777777777</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F17" s="14">
         <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>10.204081632653</v>
+        <v>58.823529411764</v>
       </c>
       <c r="I17" s="14">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J17" s="14">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.875</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.368421052631</v>
+        <v>-18.536585365853</v>
       </c>
       <c r="M17" s="15">
-        <v>145.3125</v>
+        <v>131.944444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>53.921568627451</v>
+        <v>45.217391304347</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-10</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.176470588235</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="L18" s="15">
-        <v>-65.116279069767</v>
+        <v>-65.934065934065</v>
       </c>
       <c r="M18" s="15">
-        <v>-72.477064220183</v>
+        <v>-73.275862068965</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.398773006135</v>
+        <v>-95.558739255014</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>7.017543859649</v>
+        <v>20.754716981132</v>
       </c>
       <c r="I19" s="14">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="J19" s="14">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.853403141361</v>
+        <v>-4.455445544554</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.046332046332</v>
+        <v>-30.824372759856</v>
       </c>
       <c r="M19" s="15">
-        <v>17.333333333333</v>
+        <v>24.516129032258</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.675958188153</v>
+        <v>-36.513157894736</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>10</v>
+      </c>
+      <c r="D20" s="14">
         <v>8</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>166.666666666667</v>
+        <v>25</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>212.5</v>
+        <v>60</v>
       </c>
       <c r="I20" s="14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>22.222222222222</v>
+        <v>22.641509433962</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.384615384615</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M20" s="15">
-        <v>48.648648648648</v>
+        <v>58.536585365853</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.248226950354</v>
+        <v>-89.166666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>34.210526315789</v>
+        <v>47.058823529411</v>
       </c>
       <c r="F21" s="17">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G21" s="17">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="H21" s="18">
-        <v>3.571428571428</v>
+        <v>18</v>
       </c>
       <c r="I21" s="17">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="J21" s="17">
-        <v>550</v>
+        <v>584</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.636363636363</v>
+        <v>-4.794520547945</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.443994601889</v>
+        <v>-29.797979797979</v>
       </c>
       <c r="M21" s="18">
-        <v>6.054279749478</v>
+        <v>9.664694280078</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.036855036855</v>
+        <v>-74.413253566497</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>4</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
+        <v>25</v>
+      </c>
+      <c r="I22" s="14">
+        <v>15</v>
+      </c>
+      <c r="J22" s="14">
+        <v>14</v>
+      </c>
+      <c r="K22" s="15">
+        <v>7.142857142857</v>
+      </c>
+      <c r="L22" s="15">
+        <v>7.142857142857</v>
+      </c>
+      <c r="M22" s="15">
         <v>50</v>
-      </c>
-      <c r="I22" s="14">
-        <v>16</v>
-      </c>
-      <c r="J22" s="14">
-        <v>13</v>
-      </c>
-      <c r="K22" s="15">
-        <v>23.076923076923</v>
-      </c>
-      <c r="L22" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="M22" s="15">
-        <v>77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.260869565217</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="G24" s="14">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.053763440860</v>
+        <v>-15.606936416185</v>
       </c>
       <c r="I24" s="14">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="J24" s="14">
-        <v>654</v>
+        <v>692</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.712538226299</v>
+        <v>-21.531791907514</v>
       </c>
       <c r="L24" s="15">
-        <v>-40.740740740740</v>
+        <v>-40.720524017467</v>
       </c>
       <c r="M24" s="15">
-        <v>36.170212765957</v>
+        <v>32.762836185819</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.058823529411</v>
+        <v>-28</v>
       </c>
       <c r="F25" s="14">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="G25" s="14">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.351351351351</v>
+        <v>-28.030303030303</v>
       </c>
       <c r="I25" s="14">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="J25" s="14">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.460803059273</v>
+        <v>-33.211678832116</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.568181818181</v>
+        <v>-50.938337801608</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>-11.538461538461</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G26" s="14">
         <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>3.488372093023</v>
+        <v>8.139534883720</v>
       </c>
       <c r="I26" s="14">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="J26" s="14">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="K26" s="15">
-        <v>12.121212121212</v>
+        <v>10.588235294117</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.515923566879</v>
+        <v>-17.058823529411</v>
       </c>
       <c r="M26" s="15">
-        <v>62.893081761006</v>
+        <v>62.068965517241</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>4</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-75</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>14</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="F28" s="14">
-        <v>15</v>
-      </c>
-      <c r="G28" s="14">
-        <v>8</v>
-      </c>
       <c r="H28" s="15">
-        <v>87.5</v>
+        <v>180</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.677419354838</v>
+        <v>-6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.666666666666</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,13 +1476,13 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="H29" s="15">
-        <v>100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1517,13 +1517,13 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="H30" s="15">
-        <v>100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-75</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
@@ -920,10 +920,10 @@
         <v>15.384615384615</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M15" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
         <v>400</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G16" s="14">
         <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-24.242424242424</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I16" s="14">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J16" s="14">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.5</v>
+        <v>-8.490566037735</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.235294117647</v>
+        <v>-31.205673758865</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.663716814159</v>
+        <v>-21.774193548387</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.995475113122</v>
+        <v>-79.578947368421</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14">
         <v>10</v>
       </c>
-      <c r="D17" s="14">
-        <v>7</v>
-      </c>
       <c r="E17" s="15">
-        <v>42.857142857142</v>
+        <v>-30</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>58.823529411764</v>
+        <v>37.5</v>
       </c>
       <c r="I17" s="14">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J17" s="14">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.536585365853</v>
+        <v>-22.321428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>131.944444444444</v>
+        <v>120.253164556962</v>
       </c>
       <c r="N17" s="15">
-        <v>45.217391304347</v>
+        <v>43.801652892562</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>14.285714285714</v>
+        <v>10</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.509433962264</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L18" s="15">
-        <v>-65.934065934065</v>
+        <v>-62.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.275862068965</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.558739255014</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>72.727272727272</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>20.754716981132</v>
+        <v>6.122448979591</v>
       </c>
       <c r="I19" s="14">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="J19" s="14">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.455445544554</v>
+        <v>-4.265402843601</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.824372759856</v>
+        <v>-32.890365448505</v>
       </c>
       <c r="M19" s="15">
-        <v>24.516129032258</v>
+        <v>20.238095238095</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.513157894736</v>
+        <v>-38.036809815950</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>60</v>
+        <v>64.705882352941</v>
       </c>
       <c r="I20" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>22.641509433962</v>
+        <v>24.137931034482</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.142857142857</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="M20" s="15">
-        <v>58.536585365853</v>
+        <v>50</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.166666666666</v>
+        <v>-88.589540412044</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>47.058823529411</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G21" s="17">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H21" s="18">
-        <v>18</v>
+        <v>17.931034482758</v>
       </c>
       <c r="I21" s="17">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="J21" s="17">
-        <v>584</v>
+        <v>622</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.794520547945</v>
+        <v>-4.019292604501</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.797979797979</v>
+        <v>-29.681978798586</v>
       </c>
       <c r="M21" s="18">
-        <v>9.664694280078</v>
+        <v>9.140767824497</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.413253566497</v>
+        <v>-74.099783080260</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>7.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.052631578947</v>
+        <v>23.809523809523</v>
       </c>
       <c r="F24" s="14">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="G24" s="14">
         <v>173</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.606936416185</v>
+        <v>-9.248554913294</v>
       </c>
       <c r="I24" s="14">
-        <v>543</v>
+        <v>595</v>
       </c>
       <c r="J24" s="14">
-        <v>692</v>
+        <v>734</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.531791907514</v>
+        <v>-18.937329700272</v>
       </c>
       <c r="L24" s="15">
-        <v>-40.720524017467</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="M24" s="15">
-        <v>32.762836185819</v>
+        <v>35.535307517084</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E25" s="15">
-        <v>-28</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G25" s="14">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.030303030303</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="I25" s="14">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="J25" s="14">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.211678832116</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.938337801608</v>
+        <v>-49.431099873577</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E26" s="15">
-        <v>-8.333333333333</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="F26" s="14">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G26" s="14">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H26" s="15">
-        <v>8.139534883720</v>
+        <v>-3.061224489795</v>
       </c>
       <c r="I26" s="14">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="J26" s="14">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="K26" s="15">
-        <v>10.588235294117</v>
+        <v>5.902777777777</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.058823529411</v>
+        <v>-15.277777777777</v>
       </c>
       <c r="M26" s="15">
-        <v>62.068965517241</v>
+        <v>68.508287292817</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-75</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>16</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>180</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.25</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.764705882352</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="15">
         <v>-50</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>15.384615384615</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L15" s="15">
-        <v>36.363636363636</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="N15" s="15">
-        <v>400</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>11</v>
+      </c>
+      <c r="D16" s="14">
         <v>13</v>
       </c>
-      <c r="D16" s="14">
-        <v>10</v>
-      </c>
       <c r="E16" s="15">
-        <v>30</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F16" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>3.030303030303</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J16" s="14">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.490566037735</v>
+        <v>-10.084033613445</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.205673758865</v>
+        <v>-30.065359477124</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.774193548387</v>
+        <v>-15.748031496063</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.578947368421</v>
+        <v>-78.685258964143</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
         <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-30</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>37.5</v>
+        <v>36.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="J17" s="14">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.694915254237</v>
+        <v>1.604278074866</v>
       </c>
       <c r="L17" s="15">
-        <v>-22.321428571428</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M17" s="15">
-        <v>120.253164556962</v>
+        <v>123.529411764706</v>
       </c>
       <c r="N17" s="15">
-        <v>43.801652892562</v>
+        <v>45.038167938931</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
         <v>11</v>
       </c>
-      <c r="G18" s="14">
-        <v>10</v>
-      </c>
       <c r="H18" s="15">
-        <v>10</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>-36.842105263157</v>
+        <v>-30.508474576271</v>
       </c>
       <c r="L18" s="15">
-        <v>-62.5</v>
+        <v>-59</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.230769230769</v>
+        <v>-66.393442622950</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.121951219512</v>
+        <v>-94.689119170984</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>11.111111111111</v>
+        <v>84.615384615384</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H19" s="15">
-        <v>6.122448979591</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="J19" s="14">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.265402843601</v>
+        <v>1.339285714285</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.890365448505</v>
+        <v>-30.792682926829</v>
       </c>
       <c r="M19" s="15">
-        <v>20.238095238095</v>
+        <v>26.111111111111</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.036809815950</v>
+        <v>-33.038348082595</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>64.705882352941</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I20" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>24.137931034482</v>
+        <v>23.4375</v>
       </c>
       <c r="L20" s="15">
-        <v>-2.702702702702</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>50</v>
+        <v>54.901960784313</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.589540412044</v>
+        <v>-88.261515601783</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>10.526315789473</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="G21" s="17">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H21" s="18">
-        <v>17.931034482758</v>
+        <v>32.903225806451</v>
       </c>
       <c r="I21" s="17">
-        <v>597</v>
+        <v>662</v>
       </c>
       <c r="J21" s="17">
-        <v>622</v>
+        <v>667</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.019292604501</v>
+        <v>-0.749625187406</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.681978798586</v>
+        <v>-26.688815060908</v>
       </c>
       <c r="M21" s="18">
-        <v>9.140767824497</v>
+        <v>14.930555555555</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.099783080260</v>
+        <v>-72.779605263157</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,31 +1189,31 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
       </c>
       <c r="J22" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="L22" s="15">
         <v>7.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" s="15">
-        <v>23.809523809523</v>
+        <v>35</v>
       </c>
       <c r="F24" s="14">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G24" s="14">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.248554913294</v>
+        <v>1.807228915662</v>
       </c>
       <c r="I24" s="14">
-        <v>595</v>
+        <v>649</v>
       </c>
       <c r="J24" s="14">
-        <v>734</v>
+        <v>774</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.937329700272</v>
+        <v>-16.149870801033</v>
       </c>
       <c r="L24" s="15">
-        <v>-39.285714285714</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M24" s="15">
-        <v>35.535307517084</v>
+        <v>38.675213675213</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D25" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>21.428571428571</v>
+        <v>69.565217391304</v>
       </c>
       <c r="F25" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G25" s="14">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.512195121951</v>
+        <v>-0.909090909090</v>
       </c>
       <c r="I25" s="14">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="J25" s="14">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.555555555555</v>
+        <v>-26.711185308848</v>
       </c>
       <c r="L25" s="15">
-        <v>-49.431099873577</v>
+        <v>-48.714953271028</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>-21.212121212121</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G26" s="14">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.061224489795</v>
+        <v>-17.171717171717</v>
       </c>
       <c r="I26" s="14">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="J26" s="14">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="K26" s="15">
-        <v>5.902777777777</v>
+        <v>4.605263157894</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.277777777777</v>
+        <v>-17.402597402597</v>
       </c>
       <c r="M26" s="15">
-        <v>68.508287292817</v>
+        <v>65.625</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>4</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
         <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,122 +1426,122 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14">
         <v>33</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.060606060606</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.428571428571</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>3</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F29" s="14">
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
+        <v>500</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="15">
         <v>200</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="15">
-        <v>50</v>
-      </c>
       <c r="N29" s="15">
-        <v>-85</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M30" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N30" s="15">
-        <v>-84.210526315789</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,34 +1555,34 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>42</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -885,48 +885,48 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>22</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>30.769230769230</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L15" s="15">
-        <v>54.545454545454</v>
+        <v>72.727272727272</v>
       </c>
       <c r="M15" s="15">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N15" s="15">
-        <v>325</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H16" s="15">
-        <v>5.555555555555</v>
+        <v>20.588235294117</v>
       </c>
       <c r="I16" s="14">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J16" s="14">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.084033613445</v>
+        <v>-9.375</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.065359477124</v>
+        <v>-27.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.748031496063</v>
+        <v>-10.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.685258964143</v>
+        <v>-78.518518518518</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F17" s="14">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H17" s="15">
-        <v>36.111111111111</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="I17" s="14">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J17" s="14">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="K17" s="15">
-        <v>1.604278074866</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.391304347826</v>
+        <v>-20.948616600790</v>
       </c>
       <c r="M17" s="15">
-        <v>123.529411764706</v>
+        <v>112.765957446809</v>
       </c>
       <c r="N17" s="15">
-        <v>45.038167938931</v>
+        <v>40.845070422535</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>18.181818181818</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.508474576271</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L18" s="15">
-        <v>-59</v>
+        <v>-58.095238095238</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.393442622950</v>
+        <v>-65.625</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.689119170984</v>
+        <v>-94.607843137254</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>84.615384615384</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F19" s="14">
         <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>55.555555555555</v>
+        <v>34.615384615384</v>
       </c>
       <c r="I19" s="14">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="J19" s="14">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="K19" s="15">
-        <v>1.339285714285</v>
+        <v>0.411522633744</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.792682926829</v>
+        <v>-30.085959885386</v>
       </c>
       <c r="M19" s="15">
-        <v>26.111111111111</v>
+        <v>31.891891891891</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.038348082595</v>
+        <v>-32.222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>45.454545454545</v>
+        <v>26.086956521739</v>
       </c>
       <c r="I20" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K20" s="15">
-        <v>23.4375</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-1.176470588235</v>
       </c>
       <c r="M20" s="15">
-        <v>54.901960784313</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.261515601783</v>
+        <v>-87.948350071736</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E21" s="18">
-        <v>44.444444444444</v>
+        <v>-20.338983050847</v>
       </c>
       <c r="F21" s="17">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G21" s="17">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H21" s="18">
-        <v>32.903225806451</v>
+        <v>14.772727272727</v>
       </c>
       <c r="I21" s="17">
-        <v>662</v>
+        <v>708</v>
       </c>
       <c r="J21" s="17">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.749625187406</v>
+        <v>-2.479338842975</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.688815060908</v>
+        <v>-26.632124352331</v>
       </c>
       <c r="M21" s="18">
-        <v>14.930555555555</v>
+        <v>18</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.779605263157</v>
+        <v>-72.472783825816</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>3</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J22" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>-6.25</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L22" s="15">
-        <v>7.142857142857</v>
+        <v>26.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>58.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D24" s="14">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E24" s="15">
-        <v>35</v>
+        <v>-25.423728813559</v>
       </c>
       <c r="F24" s="14">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="G24" s="14">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H24" s="15">
-        <v>1.807228915662</v>
+        <v>0.558659217877</v>
       </c>
       <c r="I24" s="14">
-        <v>649</v>
+        <v>693</v>
       </c>
       <c r="J24" s="14">
-        <v>774</v>
+        <v>833</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.149870801033</v>
+        <v>-16.806722689075</v>
       </c>
       <c r="L24" s="15">
-        <v>-38.888888888888</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="M24" s="15">
-        <v>38.675213675213</v>
+        <v>36.417322834645</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E25" s="15">
-        <v>69.565217391304</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="F25" s="14">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G25" s="14">
         <v>110</v>
       </c>
       <c r="H25" s="15">
-        <v>-0.909090909090</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I25" s="14">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="J25" s="14">
-        <v>599</v>
+        <v>633</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.711185308848</v>
+        <v>-26.856240126382</v>
       </c>
       <c r="L25" s="15">
-        <v>-48.714953271028</v>
+        <v>-48.555555555555</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G26" s="14">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.171717171717</v>
+        <v>-13.402061855670</v>
       </c>
       <c r="I26" s="14">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="J26" s="14">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="K26" s="15">
-        <v>4.605263157894</v>
+        <v>4.878048780487</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.402597402597</v>
+        <v>-16.097560975609</v>
       </c>
       <c r="M26" s="15">
-        <v>65.625</v>
+        <v>66.990291262135</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>7</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="15">
+        <v>40</v>
+      </c>
+      <c r="I27" s="14">
         <v>22</v>
       </c>
-      <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
-      <c r="H27" s="15">
-        <v>50</v>
-      </c>
-      <c r="I27" s="14">
-        <v>20</v>
-      </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="L27" s="15">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,54 +1426,54 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="14">
-        <v>10</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
         <v>33</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>-5.714285714285</v>
+        <v>2.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>3</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1494,27 +1494,27 @@
         <v>500</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M29" s="15">
         <v>200</v>
       </c>
       <c r="N29" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1523,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -1535,13 +1535,13 @@
         <v>300</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M30" s="15">
         <v>300</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-82.608695652173</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1576,13 +1576,13 @@
         <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>42</v>

--- a/data/source/weekly/cs-en-us-110pct.xlsx
+++ b/data/source/weekly/cs-en-us-110pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I15" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" s="14">
         <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>35.714285714285</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>72.727272727272</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H16" s="15">
-        <v>20.588235294117</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I16" s="14">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J16" s="14">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.375</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.5</v>
+        <v>-26.627218934911</v>
       </c>
       <c r="M16" s="15">
-        <v>-10.769230769230</v>
+        <v>-9.489051094890</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.518518518518</v>
+        <v>-78.397212543554</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>13</v>
+      </c>
+      <c r="D17" s="14">
         <v>12</v>
       </c>
-      <c r="D17" s="14">
-        <v>17</v>
-      </c>
       <c r="E17" s="15">
-        <v>-29.411764705882</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H17" s="15">
-        <v>-2.272727272727</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="I17" s="14">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="J17" s="14">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.960784313725</v>
+        <v>-1.851851851851</v>
       </c>
       <c r="L17" s="15">
-        <v>-20.948616600790</v>
+        <v>-19.696969696969</v>
       </c>
       <c r="M17" s="15">
-        <v>112.765957446809</v>
+        <v>123.157894736842</v>
       </c>
       <c r="N17" s="15">
-        <v>40.845070422535</v>
+        <v>41.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-17.647058823529</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="14">
         <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.294117647058</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.095238095238</v>
+        <v>-58.878504672897</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.625</v>
+        <v>-67.883211678832</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.607843137254</v>
+        <v>-94.805194805194</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-15.789473684210</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" s="14">
         <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>34.615384615384</v>
+        <v>25</v>
       </c>
       <c r="I19" s="14">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="J19" s="14">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="K19" s="15">
-        <v>0.411522633744</v>
+        <v>1.574803149606</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.085959885386</v>
+        <v>-28.133704735376</v>
       </c>
       <c r="M19" s="15">
-        <v>31.891891891891</v>
+        <v>32.989690721649</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.222222222222</v>
+        <v>-32.637075718015</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>25</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>26.086956521739</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J20" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K20" s="15">
-        <v>23.529411764705</v>
+        <v>29.577464788732</v>
       </c>
       <c r="L20" s="15">
-        <v>-1.176470588235</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>61.538461538461</v>
+        <v>61.403508771929</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.948350071736</v>
+        <v>-87.397260273972</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.338983050847</v>
+        <v>19.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G21" s="17">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H21" s="18">
-        <v>14.772727272727</v>
+        <v>9.550561797752</v>
       </c>
       <c r="I21" s="17">
-        <v>708</v>
+        <v>751</v>
       </c>
       <c r="J21" s="17">
-        <v>726</v>
+        <v>762</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.479338842975</v>
+        <v>-1.443569553805</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.632124352331</v>
+        <v>-25.273631840796</v>
       </c>
       <c r="M21" s="18">
-        <v>18</v>
+        <v>19.017432646592</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.472783825816</v>
+        <v>-72.216056233814</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
       </c>
       <c r="I22" s="14">
+        <v>20</v>
+      </c>
+      <c r="J22" s="14">
         <v>19</v>
       </c>
-      <c r="J22" s="14">
-        <v>17</v>
-      </c>
       <c r="K22" s="15">
-        <v>11.764705882352</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L22" s="15">
-        <v>26.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>58.333333333333</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D24" s="14">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>-25.423728813559</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
+        <v>202</v>
+      </c>
+      <c r="G24" s="14">
         <v>180</v>
       </c>
-      <c r="G24" s="14">
-        <v>179</v>
-      </c>
       <c r="H24" s="15">
-        <v>0.558659217877</v>
+        <v>12.222222222222</v>
       </c>
       <c r="I24" s="14">
-        <v>693</v>
+        <v>743</v>
       </c>
       <c r="J24" s="14">
-        <v>833</v>
+        <v>872</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.806722689075</v>
+        <v>-14.793577981651</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.735849056603</v>
+        <v>-35.837651122625</v>
       </c>
       <c r="M24" s="15">
-        <v>36.417322834645</v>
+        <v>39.924670433145</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D25" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>-32.352941176470</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G25" s="14">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H25" s="15">
-        <v>4.545454545454</v>
+        <v>11.206896551724</v>
       </c>
       <c r="I25" s="14">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="J25" s="14">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.856240126382</v>
+        <v>-25.451807228915</v>
       </c>
       <c r="L25" s="15">
-        <v>-48.555555555555</v>
+        <v>-47.171824973319</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F26" s="14">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G26" s="14">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.402061855670</v>
+        <v>-7.291666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="J26" s="14">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="K26" s="15">
-        <v>4.878048780487</v>
+        <v>4.843304843304</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.097560975609</v>
+        <v>-16.363636363636</v>
       </c>
       <c r="M26" s="15">
-        <v>66.990291262135</v>
+        <v>71.962616822429</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="14">
         <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>29.411764705882</v>
+        <v>35.294117647058</v>
       </c>
       <c r="L27" s="15">
-        <v>37.5</v>
+        <v>35.294117647058</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="I28" s="14">
+        <v>39</v>
+      </c>
+      <c r="J28" s="14">
         <v>36</v>
       </c>
-      <c r="J28" s="14">
-        <v>33</v>
-      </c>
       <c r="K28" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>2.857142857142</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>200</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>300</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.608695652173</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>3</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-66.666666666666</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
